--- a/Result/profitability/2474.xlsx
+++ b/Result/profitability/2474.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.59</v>
       </c>
       <c r="M2" t="n">
-        <v>2.88625</v>
+        <v>2.9375</v>
       </c>
       <c r="N2" t="n">
-        <v>32.025</v>
+        <v>31.31625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.67</v>
       </c>
       <c r="M3" t="n">
-        <v>2.8325</v>
+        <v>2.45625</v>
       </c>
       <c r="N3" t="n">
-        <v>33.275</v>
+        <v>32.86875000000001</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>2.34</v>
       </c>
       <c r="M4" t="n">
-        <v>2.435</v>
+        <v>2.195</v>
       </c>
       <c r="N4" t="n">
-        <v>34.53375</v>
+        <v>33.76375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,13 +1018,13 @@
         <v>1.97</v>
       </c>
       <c r="M5" t="n">
-        <v>2.1275</v>
+        <v>2.64625</v>
       </c>
       <c r="N5" t="n">
-        <v>35.01125</v>
+        <v>34.81125</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -1036,13 +1036,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>1.1</v>
       </c>
       <c r="M6" t="n">
-        <v>2.46125</v>
+        <v>2.1975</v>
       </c>
       <c r="N6" t="n">
-        <v>34.985</v>
+        <v>35.01375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.21</v>
       </c>
       <c r="M7" t="n">
-        <v>2.035</v>
+        <v>1.8775</v>
       </c>
       <c r="N7" t="n">
-        <v>35.91625</v>
+        <v>35.39875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.5</v>
       </c>
       <c r="M8" t="n">
-        <v>1.75125</v>
+        <v>1.73625</v>
       </c>
       <c r="N8" t="n">
-        <v>36.67375</v>
+        <v>36.68125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9344,27 +9344,27 @@
         <v>30.46</v>
       </c>
       <c r="G71" t="n">
-        <v>940</v>
+        <v>869</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>18.49%</t>
+          <t>17.09%</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>-1667</v>
+        <v>-1685</v>
       </c>
       <c r="J71" t="n">
-        <v>-727</v>
+        <v>-816</v>
       </c>
       <c r="K71" t="n">
-        <v>-1008</v>
+        <v>-1052</v>
       </c>
       <c r="L71" t="n">
-        <v>-1.57</v>
+        <v>-1.64</v>
       </c>
       <c r="M71" t="n">
-        <v>3.47875</v>
+        <v>3.47</v>
       </c>
       <c r="N71" t="n">
         <v>30.325</v>
@@ -9394,10 +9394,10 @@
         <v>114.2</v>
       </c>
       <c r="W71" t="n">
-        <v>-6</v>
+        <v>-6.069999999999999</v>
       </c>
       <c r="X71" t="n">
-        <v>-1.354401805869075</v>
+        <v>-1.37020316027088</v>
       </c>
       <c r="Y71" t="n">
         <v>-4.560000000000002</v>
@@ -9406,10 +9406,10 @@
         <v>-0.1302113078241006</v>
       </c>
       <c r="AA71" t="n">
-        <v>-6.62</v>
+        <v>-6.69</v>
       </c>
       <c r="AB71" t="n">
-        <v>-1.310891089108911</v>
+        <v>-1.324752475247525</v>
       </c>
       <c r="AC71" t="n">
         <v>-3.579999999999998</v>
@@ -9471,24 +9471,24 @@
         <v>28.63</v>
       </c>
       <c r="G72" t="n">
-        <v>738</v>
+        <v>810</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>15.19%</t>
+          <t>16.66%</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3048</v>
+        <v>3066</v>
       </c>
       <c r="J72" t="n">
-        <v>3786</v>
+        <v>3875</v>
       </c>
       <c r="K72" t="n">
-        <v>2883</v>
+        <v>2927</v>
       </c>
       <c r="L72" t="n">
-        <v>4.62</v>
+        <v>4.69</v>
       </c>
       <c r="M72" t="n">
         <v>3.2325</v>
@@ -9521,10 +9521,10 @@
         <v>114.3</v>
       </c>
       <c r="W72" t="n">
-        <v>6.19</v>
+        <v>6.33</v>
       </c>
       <c r="X72" t="n">
-        <v>-3.942675159235669</v>
+        <v>-3.859756097560976</v>
       </c>
       <c r="Y72" t="n">
         <v>-1.830000000000002</v>
@@ -9533,10 +9533,10 @@
         <v>-0.06007879185817466</v>
       </c>
       <c r="AA72" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.2</v>
+        <v>1.233333333333333</v>
       </c>
       <c r="AC72" t="n">
         <v>-5.900000000000002</v>
@@ -9648,10 +9648,10 @@
         <v>114.4</v>
       </c>
       <c r="W73" t="n">
-        <v>-0.8500000000000001</v>
+        <v>-0.9200000000000004</v>
       </c>
       <c r="X73" t="n">
-        <v>-0.183982683982684</v>
+        <v>-0.1961620469083156</v>
       </c>
       <c r="Y73" t="n">
         <v>4.370000000000001</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2474</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2681</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1907</v>
+      </c>
+      <c r="E75" t="n">
+        <v>774</v>
+      </c>
+      <c r="F75" t="n">
+        <v>28.86</v>
+      </c>
+      <c r="G75" t="n">
+        <v>48</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.78%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1619</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1667</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1355</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="M75" t="n">
+        <v>3.00125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>31.42625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.1200000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.04562737642585557</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.05999999999999872</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.002083333333333215</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>4.149999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-2.530487804878049</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.600000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.05252790544977026</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
